--- a/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v6/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v6/Contrary(P)Body(N).xlsx
@@ -30681,16 +30681,16 @@
         <v>97</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8964497041420119</v>
+        <v>0.89645</v>
       </c>
       <c r="M2" t="n">
         <v>0.7575</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.821138</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7098901098901099</v>
+        <v>0.70989</v>
       </c>
     </row>
     <row r="3">
@@ -30740,16 +30740,16 @@
         <v>98</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8961424332344213</v>
+        <v>0.896142</v>
       </c>
       <c r="M3" t="n">
         <v>0.755</v>
       </c>
       <c r="N3" t="n">
-        <v>0.819538670284939</v>
+        <v>0.819538</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7076923076923077</v>
+        <v>0.707692</v>
       </c>
     </row>
     <row r="4">
@@ -30799,16 +30799,16 @@
         <v>97</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8964497041420119</v>
+        <v>0.89645</v>
       </c>
       <c r="M4" t="n">
         <v>0.7575</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.821138</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7098901098901099</v>
+        <v>0.70989</v>
       </c>
     </row>
   </sheetData>
